--- a/gender_biased_words.xlsx
+++ b/gender_biased_words.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hi\Desktop\POC_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98FF3E6-5FF3-47D0-B420-588DD54B6511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DE4E491-DD40-4766-8CA0-6572C02A58A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="word" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -27,6 +38,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
+    <t>word</t>
+  </si>
+  <si>
     <t>he</t>
   </si>
   <si>
@@ -46,16 +60,13 @@
   </si>
   <si>
     <t>she</t>
-  </si>
-  <si>
-    <t>word</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,46 +378,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
